--- a/artfynd/A 42447-2020 artfynd.xlsx
+++ b/artfynd/A 42447-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42447-2020 artfynd.xlsx
+++ b/artfynd/A 42447-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81279503</v>
+        <v>61680670</v>
       </c>
       <c r="B2" t="n">
-        <v>109753</v>
+        <v>108190</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -712,20 +712,19 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvillinge socken, Häradsveden, Ög</t>
+          <t>Häradssveden, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572359</v>
+        <v>572358.6791949016</v>
       </c>
       <c r="R2" t="n">
-        <v>6506417</v>
+        <v>6506416.904137127</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,110 +746,114 @@
           <t>Kvillinge</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>E-Nor-0210</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1858-01-01</t>
+          <t>2016-08-11</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1858-12-31</t>
+          <t>2016-08-11</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Leg. Carl Swartling {ÖG. Qvillinge sn. Häradsveden, på Kolmorden. Carl Swartling}</t>
+          <t>Området har tidigare betats av får, nu igenväxande</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Biologiska Museet, Lunds Universitet</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>1170623</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Anders Svenson</t>
+          <t>bert lindgren, Mats Blomstedt, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Äldre fynd i Östergötlands flora</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61680670</v>
+        <v>88797998</v>
       </c>
       <c r="B3" t="n">
-        <v>108190</v>
+        <v>5113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1253</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Piploka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pleurospermum austriacum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Häradssveden, Ög</t>
+          <t>Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572358.6791949016</v>
+        <v>572338.5110023194</v>
       </c>
       <c r="R3" t="n">
-        <v>6506416.904137127</v>
+        <v>6506381.17643822</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,14 +875,9 @@
           <t>Kvillinge</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>E-Nor-0210</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-08-11</t>
+          <t>2020-10-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -889,7 +887,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-08-11</t>
+          <t>2020-10-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -897,13 +895,8 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Området har tidigare betats av får, nu igenväxande</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
@@ -914,26 +907,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>bert lindgren, Mats Blomstedt, Rolf Wahlström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88797998</v>
+        <v>88798193</v>
       </c>
       <c r="B4" t="n">
-        <v>5113</v>
+        <v>89794</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,37 +935,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rigidoporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrköping, Ög</t>
+          <t>Bärsjöholm 6, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572338.5110023194</v>
+        <v>572289.8678735136</v>
       </c>
       <c r="R4" t="n">
-        <v>6506381.17643822</v>
+        <v>6506588.221108335</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1045,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88798193</v>
+        <v>88798382</v>
       </c>
       <c r="B5" t="n">
-        <v>89794</v>
+        <v>89356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,35 +1048,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5321</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bärsjöholm 6, Norrköping, Ög</t>
+          <t>Häradssveden Almeberg, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572289.8678735136</v>
+        <v>572322.6496174684</v>
       </c>
       <c r="R5" t="n">
-        <v>6506588.221108335</v>
+        <v>6506561.798198648</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1158,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88798382</v>
+        <v>88798278</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
+        <v>93132</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,35 +1161,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Häradssveden Almeberg, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572322.6496174684</v>
+        <v>572349.7030237874</v>
       </c>
       <c r="R6" t="n">
-        <v>6506561.798198648</v>
+        <v>6506563.341487526</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1271,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88798278</v>
+        <v>88798603</v>
       </c>
       <c r="B7" t="n">
-        <v>93132</v>
+        <v>5113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,36 +1275,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2671</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Häradssveden Almeberg, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572349.7030237874</v>
+        <v>572370.9036760698</v>
       </c>
       <c r="R7" t="n">
-        <v>6506563.341487526</v>
+        <v>6506571.534195597</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1385,7 +1374,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88798603</v>
+        <v>88798707</v>
       </c>
       <c r="B8" t="n">
         <v>5113</v>
@@ -1428,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572370.9036760698</v>
+        <v>572418.5737217965</v>
       </c>
       <c r="R8" t="n">
-        <v>6506571.534195597</v>
+        <v>6506528.753455398</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1500,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88798707</v>
+        <v>88798214</v>
       </c>
       <c r="B9" t="n">
-        <v>5113</v>
+        <v>93132</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1516,37 +1505,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>2671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Häradssveden Almeberg, Norrköping, Ög</t>
+          <t>Bärsjöholm 6, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572418.5737217965</v>
+        <v>572311.0104874606</v>
       </c>
       <c r="R9" t="n">
-        <v>6506528.753455398</v>
+        <v>6506599.531514822</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1612,120 +1600,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>88798214</v>
-      </c>
-      <c r="B10" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>2671</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Fällmossa</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Antitrichia curtipendula</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Bärsjöholm 6, Norrköping, Ög</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>572311.0104874606</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6506599.531514822</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Kvillinge</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2020-10-30</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2020-10-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
